--- a/docs/pension_data_combined_2026-06-02.xlsx
+++ b/docs/pension_data_combined_2026-06-02.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.12" customWidth="1" min="1" max="1"/>
@@ -454,14 +454,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALLIANZ</t>
+          <t>ARTEA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allianz D1 gimusiems 2003-2009 m.</t>
+          <t>Artea pensija 2003-2009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1763</v>
+        <v>1.2243</v>
       </c>
       <c r="D3" t="n">
-        <v>2089113.59</v>
+        <v>3041679.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Allianz S turto išsaugojimo</t>
+          <t>Artea pensija 1996-2002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1836</v>
+        <v>2.318</v>
       </c>
       <c r="D4" t="n">
-        <v>35050717.09</v>
+        <v>36180414.83000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Allianz X1 gimusiems 1961–1967 m.</t>
+          <t>Artea pensija 1989-1995</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.4538</v>
+        <v>2.3011</v>
       </c>
       <c r="D5" t="n">
-        <v>187933158.67</v>
+        <v>126626987.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Allianz X2 gimusiems 1968–1974 m.</t>
+          <t>Artea pensija 1982-1988</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -524,16 +524,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.9714</v>
+        <v>2.307</v>
       </c>
       <c r="D6" t="n">
-        <v>217124499.99</v>
+        <v>234277824.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Allianz X3 gimusiems 1975–1981 m.</t>
+          <t>Artea pensija 1975-1981</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.2397</v>
+        <v>2.2845</v>
       </c>
       <c r="D7" t="n">
-        <v>222353579.03</v>
+        <v>228764648.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Allianz Y1 gimusiems 1982–1988 m.</t>
+          <t>Artea pensija 1968-1974</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2801</v>
+        <v>1.9741</v>
       </c>
       <c r="D8" t="n">
-        <v>180488052.5</v>
+        <v>169581995.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Allianz Y2 gimusiems 1989–1995 m.</t>
+          <t>Artea pensija 1961-1967</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.2753</v>
+        <v>1.5562</v>
       </c>
       <c r="D9" t="n">
-        <v>98604420.27</v>
+        <v>112117010.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Allianz Y3 gimusiems 1996–2002 m.</t>
+          <t>Artea pensijų turto išsaugojimo fondas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -596,23 +596,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.2561</v>
+        <v>1.2531</v>
       </c>
       <c r="D10" t="n">
-        <v>38143391.68</v>
+        <v>17442354.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARTEA</t>
+          <t>GOINDEX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artea pensija 2003-2009</t>
+          <t>Goindex pensija 2003-2009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.2243</v>
+        <v>1.209</v>
       </c>
       <c r="D12" t="n">
-        <v>3041679.12</v>
+        <v>4380093.122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Artea pensija 1996-2002</t>
+          <t>Goindex pensija 1996-2002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.318</v>
+        <v>1.5906</v>
       </c>
       <c r="D13" t="n">
-        <v>36180414.83000001</v>
+        <v>27890089.4838</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Artea pensija 1989-1995</t>
+          <t>Goindex pensija 1989-1995</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.3011</v>
+        <v>1.5868</v>
       </c>
       <c r="D14" t="n">
-        <v>126626987.28</v>
+        <v>50234830.3953</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artea pensija 1982-1988</t>
+          <t>Goindex pensija 1982-1988</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.307</v>
+        <v>1.5958</v>
       </c>
       <c r="D15" t="n">
-        <v>234277824.21</v>
+        <v>62132250.3608</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Artea pensija 1975-1981</t>
+          <t>Goindex pensija 1975-1981</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.2845</v>
+        <v>1.5884</v>
       </c>
       <c r="D16" t="n">
-        <v>228764648.92</v>
+        <v>56731047.9211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Artea pensija 1968-1974</t>
+          <t>Goindex pensija 1968-1974</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.9741</v>
+        <v>1.5706</v>
       </c>
       <c r="D17" t="n">
-        <v>169581995.12</v>
+        <v>37478843.4137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Artea pensija 1961-1967</t>
+          <t>Goindex pensija 1961-1967</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.5562</v>
+        <v>1.2691</v>
       </c>
       <c r="D18" t="n">
-        <v>112117010.1</v>
+        <v>10861142.4265</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Artea pensijų turto išsaugojimo fondas</t>
+          <t>Goindex pensijų turto išsaugojimo fondas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -747,614 +747,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.2531</v>
+        <v>1.0933</v>
       </c>
       <c r="D19" t="n">
-        <v>17442354.38</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GOINDEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Goindex pensija 2003-2009</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4380093.122</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1996-2002</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1.5906</v>
-      </c>
-      <c r="D22" t="n">
-        <v>27890089.4838</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1989-1995</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1.5868</v>
-      </c>
-      <c r="D23" t="n">
-        <v>50234830.3953</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1982-1988</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1.5958</v>
-      </c>
-      <c r="D24" t="n">
-        <v>62132250.3608</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1975-1981</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1.5884</v>
-      </c>
-      <c r="D25" t="n">
-        <v>56731047.9211</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1968-1974</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1.5706</v>
-      </c>
-      <c r="D26" t="n">
-        <v>37478843.4137</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Goindex pensija 1961-1967</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1.2691</v>
-      </c>
-      <c r="D27" t="n">
-        <v>10861142.4265</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Goindex pensijų turto išsaugojimo fondas</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1.0933</v>
-      </c>
-      <c r="D28" t="n">
         <v>1732684.1482</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LUMINOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Luminor 2003-2009 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1.1931</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3799083</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Luminor 1996-2002 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2.308</v>
-      </c>
-      <c r="D31" t="n">
-        <v>22250922.21</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Luminor 1989-1995 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2.2936</v>
-      </c>
-      <c r="D32" t="n">
-        <v>61532397.41</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Luminor 1982-1988 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>2.2779</v>
-      </c>
-      <c r="D33" t="n">
-        <v>118419986.82</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Luminor 1975-1981 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2.2755</v>
-      </c>
-      <c r="D34" t="n">
-        <v>128128950.18</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Luminor 1968-1974 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2.0677</v>
-      </c>
-      <c r="D35" t="n">
-        <v>112488537.59</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Luminor 1961-1967 tikslinės grupės pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1.5829</v>
-      </c>
-      <c r="D36" t="n">
-        <v>90045246.53</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Luminor pensijų turto išsaugojimo fondas</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1.1732</v>
-      </c>
-      <c r="D37" t="n">
-        <v>14696768.52</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SEB</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SEB pensija 2003-2009</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1.1878</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2569272</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SEB pensija 1996-2002</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2.361</v>
-      </c>
-      <c r="D40" t="n">
-        <v>47478715</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SEB pensija 1989-1995</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2.3396</v>
-      </c>
-      <c r="D41" t="n">
-        <v>156107581</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SEB pensija 1982-1988</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2.344</v>
-      </c>
-      <c r="D42" t="n">
-        <v>379248422</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SEB pensija 1975-1981</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2.3755</v>
-      </c>
-      <c r="D43" t="n">
-        <v>483571498</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SEB pensija 1968-1974</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2.0472</v>
-      </c>
-      <c r="D44" t="n">
-        <v>395051032</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SEB pensija 1961-1967</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1.5593</v>
-      </c>
-      <c r="D45" t="n">
-        <v>296053088</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SEB turto išsaugojimo fondas</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1.2163</v>
-      </c>
-      <c r="D46" t="n">
-        <v>58477090</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SWEDBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pensija 2003-2009</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1.1407</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3754475.99</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Pensija 1996-2002</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2.1448</v>
-      </c>
-      <c r="D49" t="n">
-        <v>84056413.44</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pensija 1989-1995</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2.1639</v>
-      </c>
-      <c r="D50" t="n">
-        <v>270470869.9</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pensija 1982-1988</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2.1818</v>
-      </c>
-      <c r="D51" t="n">
-        <v>412349097.6</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Pensija 1975-1981</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2.1862</v>
-      </c>
-      <c r="D52" t="n">
-        <v>502421012.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Pensija 1968-1974</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1.9718</v>
-      </c>
-      <c r="D53" t="n">
-        <v>468994312.2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pensija 1961-1967</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1.5474</v>
-      </c>
-      <c r="D54" t="n">
-        <v>369812068</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Turto išsaugojimo pensijų fondas</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.2068</v>
-      </c>
-      <c r="D55" t="n">
-        <v>68690574.45999999</v>
       </c>
     </row>
   </sheetData>
